--- a/5/search/FY2_Missile2_results/top10_solutions.xlsx
+++ b/5/search/FY2_Missile2_results/top10_solutions.xlsx
@@ -487,7 +487,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="B2" t="n">
         <v>140</v>
@@ -496,168 +496,168 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>12087.60330042253</v>
+        <v>11670.84025871621</v>
       </c>
       <c r="F2" t="n">
-        <v>846.8945292667229</v>
+        <v>946.9504831500294</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>12153.30577573943</v>
+        <v>11259.39058211148</v>
       </c>
       <c r="I2" t="n">
-        <v>432.065426216765</v>
+        <v>380.6385870875663</v>
       </c>
       <c r="J2" t="n">
-        <v>1355.9</v>
+        <v>1277.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B3" t="n">
-        <v>131.6</v>
+        <v>102</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>11837.33345416103</v>
+        <v>11423.00086655178</v>
       </c>
       <c r="F3" t="n">
-        <v>899.3638498222313</v>
+        <v>823.0008665517772</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>11674.66690832205</v>
+        <v>10990.25151646561</v>
       </c>
       <c r="I3" t="n">
-        <v>398.7276996444625</v>
+        <v>390.2515164656102</v>
       </c>
       <c r="J3" t="n">
-        <v>1321.6</v>
+        <v>1223.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.800000000000002</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>297</v>
+        <v>252</v>
       </c>
       <c r="B4" t="n">
-        <v>92.40000000000001</v>
+        <v>132</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>12503.38466611121</v>
+        <v>11836.83902697003</v>
       </c>
       <c r="F4" t="n">
-        <v>412.0519659799374</v>
+        <v>897.8421593961589</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>12503.38466611121</v>
+        <v>11673.67805394006</v>
       </c>
       <c r="I4" t="n">
-        <v>412.0519659799374</v>
+        <v>395.6843187923178</v>
       </c>
       <c r="J4" t="n">
-        <v>1400</v>
+        <v>1321.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.800000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B5" t="n">
-        <v>103.6</v>
+        <v>140</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>12256.11328493796</v>
+        <v>12087.60330042253</v>
       </c>
       <c r="F5" t="n">
-        <v>611.7643592945767</v>
+        <v>846.8945292667229</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>12320.14160617244</v>
+        <v>12153.30577573943</v>
       </c>
       <c r="I5" t="n">
-        <v>414.7054491182209</v>
+        <v>432.065426216765</v>
       </c>
       <c r="J5" t="n">
-        <v>1380.4</v>
+        <v>1355.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.800000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>297</v>
+        <v>265.5</v>
       </c>
       <c r="B6" t="n">
-        <v>137.2</v>
+        <v>122</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>12498.29997251413</v>
+        <v>11961.71196128481</v>
       </c>
       <c r="F6" t="n">
-        <v>422.0312390508474</v>
+        <v>913.5043411382335</v>
       </c>
       <c r="G6" t="n">
         <v>1400</v>
       </c>
       <c r="H6" t="n">
-        <v>12498.29997251413</v>
+        <v>11923.42392256962</v>
       </c>
       <c r="I6" t="n">
-        <v>422.0312390508474</v>
+        <v>427.008682276467</v>
       </c>
       <c r="J6" t="n">
-        <v>1400</v>
+        <v>1321.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.699999999999999</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>261</v>
       </c>
       <c r="B7" t="n">
-        <v>123.2</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -674,33 +674,33 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>11922.90909562817</v>
+        <v>11922.40850534004</v>
       </c>
       <c r="F7" t="n">
-        <v>913.2671857547161</v>
+        <v>910.1065830648117</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>11845.81819125635</v>
+        <v>11844.81701068009</v>
       </c>
       <c r="I7" t="n">
-        <v>426.5343715094323</v>
+        <v>420.2131661296235</v>
       </c>
       <c r="J7" t="n">
         <v>1321.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.699999999999999</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>288</v>
+        <v>292.5</v>
       </c>
       <c r="B8" t="n">
-        <v>131.6</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
@@ -709,95 +709,95 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>12325.33309167795</v>
+        <v>12410.23663949538</v>
       </c>
       <c r="F8" t="n">
-        <v>398.7276996444623</v>
+        <v>409.6011411479008</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>12325.33309167795</v>
+        <v>12410.23663949538</v>
       </c>
       <c r="I8" t="n">
-        <v>398.7276996444623</v>
+        <v>409.6011411479008</v>
       </c>
       <c r="J8" t="n">
         <v>1400</v>
       </c>
       <c r="K8" t="n">
-        <v>3.699999999999999</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>234</v>
+        <v>301.5</v>
       </c>
       <c r="B9" t="n">
         <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>11670.84025871621</v>
+        <v>12585.19839248186</v>
       </c>
       <c r="F9" t="n">
-        <v>946.9504831500294</v>
+        <v>445.0430159234169</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>11259.39058211148</v>
+        <v>12585.19839248186</v>
       </c>
       <c r="I9" t="n">
-        <v>380.6385870875663</v>
+        <v>445.0430159234169</v>
       </c>
       <c r="J9" t="n">
-        <v>1277.5</v>
+        <v>1400</v>
       </c>
       <c r="K9" t="n">
-        <v>3.600000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="B10" t="n">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>11894.87603949296</v>
+        <v>12443.0947277458</v>
       </c>
       <c r="F10" t="n">
-        <v>736.2734351200675</v>
+        <v>530.3776323921528</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>11842.31405923945</v>
+        <v>12498.48156871402</v>
       </c>
       <c r="I10" t="n">
-        <v>404.4101526801012</v>
+        <v>421.6748364411719</v>
       </c>
       <c r="J10" t="n">
-        <v>1321.6</v>
+        <v>1395.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -805,34 +805,34 @@
         <v>297</v>
       </c>
       <c r="B11" t="n">
-        <v>120.4</v>
+        <v>136</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>12437.28364934913</v>
+        <v>12493.94166371663</v>
       </c>
       <c r="F11" t="n">
-        <v>541.7825159017639</v>
+        <v>430.5849016830556</v>
       </c>
       <c r="G11" t="n">
         <v>1400</v>
       </c>
       <c r="H11" t="n">
-        <v>12491.94410551777</v>
+        <v>12493.94166371663</v>
       </c>
       <c r="I11" t="n">
-        <v>434.5053303894844</v>
+        <v>430.5849016830556</v>
       </c>
       <c r="J11" t="n">
-        <v>1395.1</v>
+        <v>1400</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
